--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130449955</v>
       </c>
       <c r="B2" t="n">
-        <v>80330</v>
+        <v>80333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91687</v>
+        <v>91690</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96234</v>
+        <v>96237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130449939</v>
       </c>
       <c r="B5" t="n">
-        <v>78581</v>
+        <v>78584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>95991</v>
+        <v>95994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130449955</v>
       </c>
       <c r="B2" t="n">
-        <v>80333</v>
+        <v>80359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91690</v>
+        <v>91716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96237</v>
+        <v>96263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130449939</v>
       </c>
       <c r="B5" t="n">
-        <v>78584</v>
+        <v>78610</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>95994</v>
+        <v>96020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91716</v>
+        <v>91717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96263</v>
+        <v>96264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>96020</v>
+        <v>96021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91717</v>
+        <v>91718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96264</v>
+        <v>96265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>96021</v>
+        <v>96022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130449955</v>
       </c>
       <c r="B2" t="n">
-        <v>80359</v>
+        <v>80361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91718</v>
+        <v>91720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96265</v>
+        <v>96267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130449939</v>
       </c>
       <c r="B5" t="n">
-        <v>78610</v>
+        <v>78612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>96022</v>
+        <v>96024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96267</v>
+        <v>96271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>96024</v>
+        <v>96028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130449955</v>
       </c>
       <c r="B2" t="n">
-        <v>80361</v>
+        <v>80369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91720</v>
+        <v>91732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96271</v>
+        <v>96284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130449939</v>
       </c>
       <c r="B5" t="n">
-        <v>78612</v>
+        <v>78620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>96028</v>
+        <v>96041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130449955</v>
       </c>
       <c r="B2" t="n">
-        <v>80369</v>
+        <v>80370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91732</v>
+        <v>91733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96284</v>
+        <v>96285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130449939</v>
       </c>
       <c r="B5" t="n">
-        <v>78620</v>
+        <v>78621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>96041</v>
+        <v>96042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130449955</v>
       </c>
       <c r="B2" t="n">
-        <v>80370</v>
+        <v>80371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91733</v>
+        <v>91734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96285</v>
+        <v>96288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130449939</v>
       </c>
       <c r="B5" t="n">
-        <v>78621</v>
+        <v>78622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>96042</v>
+        <v>96045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>130449982</v>
       </c>
       <c r="B3" t="n">
-        <v>91734</v>
+        <v>91742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130449977</v>
       </c>
       <c r="B4" t="n">
-        <v>96288</v>
+        <v>96297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130449916</v>
       </c>
       <c r="B6" t="n">
-        <v>96045</v>
+        <v>96054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58927-2022 artfynd.xlsx
+++ b/artfynd/A 58927-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130449955</v>
+        <v>130449821</v>
       </c>
       <c r="B2" t="n">
-        <v>80385</v>
+        <v>91460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229504</v>
+        <v>937</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567440</v>
+        <v>567451</v>
       </c>
       <c r="R2" t="n">
-        <v>6424263</v>
+        <v>6424196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Ek</t>
+          <t>Asplåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130449982</v>
+        <v>130449822</v>
       </c>
       <c r="B3" t="n">
-        <v>91756</v>
+        <v>91460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5445</v>
+        <v>937</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567437</v>
+        <v>567420</v>
       </c>
       <c r="R3" t="n">
-        <v>6424240</v>
+        <v>6424363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130449977</v>
+        <v>130449837</v>
       </c>
       <c r="B4" t="n">
-        <v>96311</v>
+        <v>97811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567435</v>
+        <v>567450</v>
       </c>
       <c r="R4" t="n">
-        <v>6424329</v>
+        <v>6424294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130449939</v>
+        <v>130449876</v>
       </c>
       <c r="B5" t="n">
-        <v>78636</v>
+        <v>96437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6436</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567440</v>
+        <v>567450</v>
       </c>
       <c r="R5" t="n">
-        <v>6424263</v>
+        <v>6424294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,11 +1052,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Ek</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130449916</v>
+        <v>130449977</v>
       </c>
       <c r="B6" t="n">
-        <v>96068</v>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomodon longifolius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schleich. ex Brid.) Hartm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567436</v>
+        <v>567435</v>
       </c>
       <c r="R6" t="n">
-        <v>6424258</v>
+        <v>6424329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1162,807 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130449916</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96183</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2674</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Liten baronmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anomodon longifolius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schleich. ex Brid.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Näringe, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567436</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6424258</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130449946</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Näringe, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567449</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6424295</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130449982</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Näringe, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567437</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6424240</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130449939</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Näringe, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567440</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6424263</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130449894</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Näringe, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567444</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6424228</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130449895</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Näringe, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567445</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6424224</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130450011</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79583</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Näringe, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567448</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6424260</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130449955</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Näringe, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567440</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6424263</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
